--- a/artfynd/A 29121-2024 artfynd.xlsx
+++ b/artfynd/A 29121-2024 artfynd.xlsx
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131736044</v>
+        <v>131736365</v>
       </c>
       <c r="B10" t="n">
-        <v>91848</v>
+        <v>80231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,19 +1494,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>388</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1514,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>714023</v>
+        <v>714004</v>
       </c>
       <c r="R10" t="n">
-        <v>7195742</v>
+        <v>7195594</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131736365</v>
+        <v>131736044</v>
       </c>
       <c r="B11" t="n">
-        <v>80231</v>
+        <v>91848</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1591,23 +1595,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>388</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Arnold) Du Rietz</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>714004</v>
+        <v>714023</v>
       </c>
       <c r="R11" t="n">
-        <v>7195594</v>
+        <v>7195742</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131736367</v>
+        <v>131736370</v>
       </c>
       <c r="B13" t="n">
         <v>80231</v>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>714002</v>
+        <v>714012</v>
       </c>
       <c r="R13" t="n">
-        <v>7195588</v>
+        <v>7195603</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,7 +1883,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131736370</v>
+        <v>131736367</v>
       </c>
       <c r="B14" t="n">
         <v>80231</v>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>714012</v>
+        <v>714002</v>
       </c>
       <c r="R14" t="n">
-        <v>7195603</v>
+        <v>7195588</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131740540</v>
+        <v>131740539</v>
       </c>
       <c r="B15" t="n">
         <v>91839</v>
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>714012</v>
+        <v>714005</v>
       </c>
       <c r="R15" t="n">
-        <v>7195598</v>
+        <v>7195586</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2085,10 +2085,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131740576</v>
+        <v>131740540</v>
       </c>
       <c r="B16" t="n">
-        <v>106145</v>
+        <v>91839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2096,21 +2096,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>1205</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>714009</v>
+        <v>714012</v>
       </c>
       <c r="R16" t="n">
-        <v>7195593</v>
+        <v>7195598</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131740539</v>
+        <v>131740576</v>
       </c>
       <c r="B17" t="n">
-        <v>91839</v>
+        <v>106145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,21 +2197,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1205</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>714005</v>
+        <v>714009</v>
       </c>
       <c r="R17" t="n">
-        <v>7195586</v>
+        <v>7195593</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2994,10 +2994,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131736269</v>
+        <v>131738027</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,21 +3005,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>713966</v>
+        <v>714054</v>
       </c>
       <c r="R25" t="n">
-        <v>7195529</v>
+        <v>7195699</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3095,10 +3095,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131738027</v>
+        <v>131736269</v>
       </c>
       <c r="B26" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>714054</v>
+        <v>713966</v>
       </c>
       <c r="R26" t="n">
-        <v>7195699</v>
+        <v>7195529</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3196,32 +3196,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131737497</v>
+        <v>131738026</v>
       </c>
       <c r="B27" t="n">
-        <v>96254</v>
+        <v>80365</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>714015</v>
+        <v>714025</v>
       </c>
       <c r="R27" t="n">
-        <v>7195628</v>
+        <v>7195680</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131738026</v>
+        <v>131736366</v>
       </c>
       <c r="B28" t="n">
-        <v>80365</v>
+        <v>80231</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3308,21 +3308,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>714025</v>
+        <v>714010</v>
       </c>
       <c r="R28" t="n">
-        <v>7195680</v>
+        <v>7195585</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3398,32 +3398,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131736366</v>
+        <v>131737497</v>
       </c>
       <c r="B29" t="n">
-        <v>80231</v>
+        <v>96254</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>388</v>
+        <v>2809</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>714010</v>
+        <v>714015</v>
       </c>
       <c r="R29" t="n">
-        <v>7195585</v>
+        <v>7195628</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,32 +3499,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131738578</v>
+        <v>131740421</v>
       </c>
       <c r="B30" t="n">
-        <v>92016</v>
+        <v>80394</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1588</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>714013</v>
+        <v>713954</v>
       </c>
       <c r="R30" t="n">
-        <v>7195670</v>
+        <v>7195561</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,32 +3600,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131740421</v>
+        <v>131738578</v>
       </c>
       <c r="B31" t="n">
-        <v>80394</v>
+        <v>92016</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>1588</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>713954</v>
+        <v>714013</v>
       </c>
       <c r="R31" t="n">
-        <v>7195561</v>
+        <v>7195670</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3802,32 +3802,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131736268</v>
+        <v>131737494</v>
       </c>
       <c r="B33" t="n">
-        <v>79260</v>
+        <v>96254</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>713898</v>
+        <v>713914</v>
       </c>
       <c r="R33" t="n">
-        <v>7195665</v>
+        <v>7195565</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4004,32 +4004,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131737494</v>
+        <v>131736268</v>
       </c>
       <c r="B35" t="n">
-        <v>96254</v>
+        <v>79260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>713914</v>
+        <v>713898</v>
       </c>
       <c r="R35" t="n">
-        <v>7195565</v>
+        <v>7195665</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 29121-2024 artfynd.xlsx
+++ b/artfynd/A 29121-2024 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131740575</v>
+        <v>131734797</v>
       </c>
       <c r="B2" t="n">
-        <v>106145</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nymyrbäcken Sydost, Vb</t>
+          <t>Nymyran Öst, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713929</v>
+        <v>714013</v>
       </c>
       <c r="R2" t="n">
-        <v>7195549</v>
+        <v>7195627</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131734797</v>
+        <v>131740575</v>
       </c>
       <c r="B3" t="n">
-        <v>99034</v>
+        <v>106146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nymyran Öst, Vb</t>
+          <t>Nymyrbäcken Sydost, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>714013</v>
+        <v>713929</v>
       </c>
       <c r="R3" t="n">
-        <v>7195627</v>
+        <v>7195549</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
         <v>131737496</v>
       </c>
       <c r="B4" t="n">
-        <v>96254</v>
+        <v>96255</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131736695</v>
       </c>
       <c r="B5" t="n">
-        <v>80269</v>
+        <v>80270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131740659</v>
+        <v>131739484</v>
       </c>
       <c r="B6" t="n">
-        <v>83240</v>
+        <v>91829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713964</v>
+        <v>714029</v>
       </c>
       <c r="R6" t="n">
-        <v>7195533</v>
+        <v>7195738</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131739484</v>
+        <v>131740659</v>
       </c>
       <c r="B7" t="n">
-        <v>91828</v>
+        <v>83241</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>714029</v>
+        <v>713964</v>
       </c>
       <c r="R7" t="n">
-        <v>7195738</v>
+        <v>7195533</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
         <v>131734796</v>
       </c>
       <c r="B8" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>131736368</v>
       </c>
       <c r="B9" t="n">
-        <v>80231</v>
+        <v>80232</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>131736365</v>
       </c>
       <c r="B10" t="n">
-        <v>80231</v>
+        <v>80232</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131736044</v>
       </c>
       <c r="B11" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>131732973</v>
       </c>
       <c r="B12" t="n">
-        <v>80400</v>
+        <v>80401</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>131736370</v>
       </c>
       <c r="B13" t="n">
-        <v>80231</v>
+        <v>80232</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>131736367</v>
       </c>
       <c r="B14" t="n">
-        <v>80231</v>
+        <v>80232</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131740539</v>
+        <v>131740576</v>
       </c>
       <c r="B15" t="n">
-        <v>91839</v>
+        <v>106146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1995,21 +1995,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1205</v>
+        <v>221725</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>714005</v>
+        <v>714009</v>
       </c>
       <c r="R15" t="n">
-        <v>7195586</v>
+        <v>7195593</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2085,10 +2085,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131740540</v>
+        <v>131740539</v>
       </c>
       <c r="B16" t="n">
-        <v>91839</v>
+        <v>91840</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>714012</v>
+        <v>714005</v>
       </c>
       <c r="R16" t="n">
-        <v>7195598</v>
+        <v>7195586</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131740576</v>
+        <v>131740540</v>
       </c>
       <c r="B17" t="n">
-        <v>106145</v>
+        <v>91840</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,21 +2197,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>1205</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>714009</v>
+        <v>714012</v>
       </c>
       <c r="R17" t="n">
-        <v>7195593</v>
+        <v>7195598</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,7 +2290,7 @@
         <v>131738024</v>
       </c>
       <c r="B18" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2388,45 +2388,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737493</v>
+        <v>131736369</v>
       </c>
       <c r="B19" t="n">
-        <v>96254</v>
+        <v>80232</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>388</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nymyrbäcken Sydost, Vb</t>
+          <t>Nymyran Öst, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>713904</v>
+        <v>714013</v>
       </c>
       <c r="R19" t="n">
-        <v>7195596</v>
+        <v>7195603</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,45 +2489,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131734798</v>
+        <v>131737493</v>
       </c>
       <c r="B20" t="n">
-        <v>99034</v>
+        <v>96255</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nymyran Öst, Vb</t>
+          <t>Nymyrbäcken Sydost, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>714024</v>
+        <v>713904</v>
       </c>
       <c r="R20" t="n">
-        <v>7195735</v>
+        <v>7195596</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2590,32 +2590,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131736369</v>
+        <v>131734798</v>
       </c>
       <c r="B21" t="n">
-        <v>80231</v>
+        <v>99035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>714013</v>
+        <v>714024</v>
       </c>
       <c r="R21" t="n">
-        <v>7195603</v>
+        <v>7195735</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131740660</v>
+        <v>131739483</v>
       </c>
       <c r="B22" t="n">
-        <v>83240</v>
+        <v>91829</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2702,21 +2702,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>714030</v>
+        <v>714033</v>
       </c>
       <c r="R22" t="n">
-        <v>7195687</v>
+        <v>7195582</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131739483</v>
+        <v>131740660</v>
       </c>
       <c r="B23" t="n">
-        <v>91828</v>
+        <v>83241</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,21 +2803,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>714033</v>
+        <v>714030</v>
       </c>
       <c r="R23" t="n">
-        <v>7195582</v>
+        <v>7195687</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2896,7 +2896,7 @@
         <v>131736364</v>
       </c>
       <c r="B24" t="n">
-        <v>80231</v>
+        <v>80232</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>131738027</v>
       </c>
       <c r="B25" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>131736269</v>
       </c>
       <c r="B26" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3196,10 +3196,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131738026</v>
+        <v>131736366</v>
       </c>
       <c r="B27" t="n">
-        <v>80365</v>
+        <v>80232</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3207,21 +3207,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>714025</v>
+        <v>714010</v>
       </c>
       <c r="R27" t="n">
-        <v>7195680</v>
+        <v>7195585</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131736366</v>
+        <v>131738026</v>
       </c>
       <c r="B28" t="n">
-        <v>80231</v>
+        <v>80366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3308,21 +3308,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>714010</v>
+        <v>714025</v>
       </c>
       <c r="R28" t="n">
-        <v>7195585</v>
+        <v>7195680</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3401,7 +3401,7 @@
         <v>131737497</v>
       </c>
       <c r="B29" t="n">
-        <v>96254</v>
+        <v>96255</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>131740421</v>
       </c>
       <c r="B30" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>131738578</v>
       </c>
       <c r="B31" t="n">
-        <v>92016</v>
+        <v>92017</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3701,45 +3701,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131740422</v>
+        <v>131736268</v>
       </c>
       <c r="B32" t="n">
-        <v>80394</v>
+        <v>79261</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nymyran Öst, Vb</t>
+          <t>Nymyrbäcken Sydost, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>714023</v>
+        <v>713898</v>
       </c>
       <c r="R32" t="n">
-        <v>7195678</v>
+        <v>7195665</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3802,45 +3802,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737494</v>
+        <v>131738025</v>
       </c>
       <c r="B33" t="n">
-        <v>96254</v>
+        <v>80366</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nymyrbäcken Sydost, Vb</t>
+          <t>Nymyran Öst, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>713914</v>
+        <v>714035</v>
       </c>
       <c r="R33" t="n">
-        <v>7195565</v>
+        <v>7195666</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3903,32 +3903,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131738025</v>
+        <v>131740422</v>
       </c>
       <c r="B34" t="n">
-        <v>80365</v>
+        <v>80395</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>714035</v>
+        <v>714023</v>
       </c>
       <c r="R34" t="n">
-        <v>7195666</v>
+        <v>7195678</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4004,32 +4004,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131736268</v>
+        <v>131737494</v>
       </c>
       <c r="B35" t="n">
-        <v>79260</v>
+        <v>96255</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>713898</v>
+        <v>713914</v>
       </c>
       <c r="R35" t="n">
-        <v>7195665</v>
+        <v>7195565</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4108,7 +4108,7 @@
         <v>131737495</v>
       </c>
       <c r="B36" t="n">
-        <v>96254</v>
+        <v>96255</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 29121-2024 artfynd.xlsx
+++ b/artfynd/A 29121-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734797</v>
       </c>
       <c r="B2" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131740575</v>
       </c>
       <c r="B3" t="n">
-        <v>106146</v>
+        <v>106144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131737496</v>
       </c>
       <c r="B4" t="n">
-        <v>96255</v>
+        <v>96258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131736695</v>
       </c>
       <c r="B5" t="n">
-        <v>80270</v>
+        <v>80273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>131739484</v>
       </c>
       <c r="B6" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>131740659</v>
       </c>
       <c r="B7" t="n">
-        <v>83241</v>
+        <v>83244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>131734796</v>
       </c>
       <c r="B8" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>131736368</v>
       </c>
       <c r="B9" t="n">
-        <v>80232</v>
+        <v>80235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>131736365</v>
       </c>
       <c r="B10" t="n">
-        <v>80232</v>
+        <v>80235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131736044</v>
       </c>
       <c r="B11" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,32 +1681,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131732973</v>
+        <v>131736370</v>
       </c>
       <c r="B12" t="n">
-        <v>80401</v>
+        <v>80235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>388</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1716,10 +1716,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>714024</v>
+        <v>714012</v>
       </c>
       <c r="R12" t="n">
-        <v>7195679</v>
+        <v>7195603</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131736370</v>
+        <v>131736367</v>
       </c>
       <c r="B13" t="n">
-        <v>80232</v>
+        <v>80235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>714012</v>
+        <v>714002</v>
       </c>
       <c r="R13" t="n">
-        <v>7195603</v>
+        <v>7195588</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,32 +1883,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131736367</v>
+        <v>131732973</v>
       </c>
       <c r="B14" t="n">
-        <v>80232</v>
+        <v>80404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>388</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>714002</v>
+        <v>714024</v>
       </c>
       <c r="R14" t="n">
-        <v>7195588</v>
+        <v>7195679</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
         <v>131740576</v>
       </c>
       <c r="B15" t="n">
-        <v>106146</v>
+        <v>106144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>131740539</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91843</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>131740540</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>91843</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,45 +2287,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131738024</v>
+        <v>131737493</v>
       </c>
       <c r="B18" t="n">
-        <v>80366</v>
+        <v>96258</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nymyran Öst, Vb</t>
+          <t>Nymyrbäcken Sydost, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>713955</v>
+        <v>713904</v>
       </c>
       <c r="R18" t="n">
-        <v>7195559</v>
+        <v>7195596</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131736369</v>
+        <v>131738024</v>
       </c>
       <c r="B19" t="n">
-        <v>80232</v>
+        <v>80369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,21 +2399,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>714013</v>
+        <v>713955</v>
       </c>
       <c r="R19" t="n">
-        <v>7195603</v>
+        <v>7195559</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,45 +2489,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131737493</v>
+        <v>131736369</v>
       </c>
       <c r="B20" t="n">
-        <v>96255</v>
+        <v>80235</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>388</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nymyrbäcken Sydost, Vb</t>
+          <t>Nymyran Öst, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>713904</v>
+        <v>714013</v>
       </c>
       <c r="R20" t="n">
-        <v>7195596</v>
+        <v>7195603</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2593,7 +2593,7 @@
         <v>131734798</v>
       </c>
       <c r="B21" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>131739483</v>
       </c>
       <c r="B22" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>131740660</v>
       </c>
       <c r="B23" t="n">
-        <v>83241</v>
+        <v>83244</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>131736364</v>
       </c>
       <c r="B24" t="n">
-        <v>80232</v>
+        <v>80235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131738027</v>
+        <v>131736269</v>
       </c>
       <c r="B25" t="n">
-        <v>80366</v>
+        <v>79264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,21 +3005,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>714054</v>
+        <v>713966</v>
       </c>
       <c r="R25" t="n">
-        <v>7195699</v>
+        <v>7195529</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3095,10 +3095,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131736269</v>
+        <v>131738027</v>
       </c>
       <c r="B26" t="n">
-        <v>79261</v>
+        <v>80369</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>713966</v>
+        <v>714054</v>
       </c>
       <c r="R26" t="n">
-        <v>7195529</v>
+        <v>7195699</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
         <v>131736366</v>
       </c>
       <c r="B27" t="n">
-        <v>80232</v>
+        <v>80235</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,32 +3297,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131738026</v>
+        <v>131737497</v>
       </c>
       <c r="B28" t="n">
-        <v>80366</v>
+        <v>96258</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>714025</v>
+        <v>714015</v>
       </c>
       <c r="R28" t="n">
-        <v>7195680</v>
+        <v>7195628</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3398,32 +3398,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131737497</v>
+        <v>131738026</v>
       </c>
       <c r="B29" t="n">
-        <v>96255</v>
+        <v>80369</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>714015</v>
+        <v>714025</v>
       </c>
       <c r="R29" t="n">
-        <v>7195628</v>
+        <v>7195680</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,32 +3499,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131740421</v>
+        <v>131738578</v>
       </c>
       <c r="B30" t="n">
-        <v>80395</v>
+        <v>92020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>1588</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>713954</v>
+        <v>714013</v>
       </c>
       <c r="R30" t="n">
-        <v>7195561</v>
+        <v>7195670</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,32 +3600,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131738578</v>
+        <v>131740421</v>
       </c>
       <c r="B31" t="n">
-        <v>92017</v>
+        <v>80398</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1588</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>714013</v>
+        <v>713954</v>
       </c>
       <c r="R31" t="n">
-        <v>7195670</v>
+        <v>7195561</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131736268</v>
+        <v>131738025</v>
       </c>
       <c r="B32" t="n">
-        <v>79261</v>
+        <v>80369</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3712,34 +3712,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nymyrbäcken Sydost, Vb</t>
+          <t>Nymyran Öst, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>713898</v>
+        <v>714035</v>
       </c>
       <c r="R32" t="n">
-        <v>7195665</v>
+        <v>7195666</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3802,32 +3802,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131738025</v>
+        <v>131740422</v>
       </c>
       <c r="B33" t="n">
-        <v>80366</v>
+        <v>80398</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>714035</v>
+        <v>714023</v>
       </c>
       <c r="R33" t="n">
-        <v>7195666</v>
+        <v>7195678</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3903,45 +3903,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131740422</v>
+        <v>131736268</v>
       </c>
       <c r="B34" t="n">
-        <v>80395</v>
+        <v>79264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nymyran Öst, Vb</t>
+          <t>Nymyrbäcken Sydost, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>714023</v>
+        <v>713898</v>
       </c>
       <c r="R34" t="n">
-        <v>7195678</v>
+        <v>7195665</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4007,7 +4007,7 @@
         <v>131737494</v>
       </c>
       <c r="B35" t="n">
-        <v>96255</v>
+        <v>96258</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>131737495</v>
       </c>
       <c r="B36" t="n">
-        <v>96255</v>
+        <v>96258</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 29121-2024 artfynd.xlsx
+++ b/artfynd/A 29121-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734797</v>
       </c>
       <c r="B2" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131740575</v>
       </c>
       <c r="B3" t="n">
-        <v>106204</v>
+        <v>106207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131737496</v>
       </c>
       <c r="B4" t="n">
-        <v>96315</v>
+        <v>96318</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131736695</v>
       </c>
       <c r="B5" t="n">
-        <v>80324</v>
+        <v>80326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>131739484</v>
       </c>
       <c r="B6" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>131740659</v>
       </c>
       <c r="B7" t="n">
-        <v>83295</v>
+        <v>83297</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>131734796</v>
       </c>
       <c r="B8" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>131736368</v>
       </c>
       <c r="B9" t="n">
-        <v>80286</v>
+        <v>80288</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131736365</v>
+        <v>131736044</v>
       </c>
       <c r="B10" t="n">
-        <v>80286</v>
+        <v>91912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,23 +1494,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>388</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Arnold) Du Rietz</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1518,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>714004</v>
+        <v>714023</v>
       </c>
       <c r="R10" t="n">
-        <v>7195594</v>
+        <v>7195742</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,10 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131736044</v>
+        <v>131736365</v>
       </c>
       <c r="B11" t="n">
-        <v>91909</v>
+        <v>80288</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,19 +1591,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>388</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>714023</v>
+        <v>714004</v>
       </c>
       <c r="R11" t="n">
-        <v>7195742</v>
+        <v>7195594</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1681,32 +1681,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131732973</v>
+        <v>131736370</v>
       </c>
       <c r="B12" t="n">
-        <v>80455</v>
+        <v>80288</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>388</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1716,10 +1716,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>714024</v>
+        <v>714012</v>
       </c>
       <c r="R12" t="n">
-        <v>7195679</v>
+        <v>7195603</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131736370</v>
+        <v>131736367</v>
       </c>
       <c r="B13" t="n">
-        <v>80286</v>
+        <v>80288</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>714012</v>
+        <v>714002</v>
       </c>
       <c r="R13" t="n">
-        <v>7195603</v>
+        <v>7195588</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,32 +1883,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131736367</v>
+        <v>131732973</v>
       </c>
       <c r="B14" t="n">
-        <v>80286</v>
+        <v>80457</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>388</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>714002</v>
+        <v>714024</v>
       </c>
       <c r="R14" t="n">
-        <v>7195588</v>
+        <v>7195679</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
         <v>131740576</v>
       </c>
       <c r="B15" t="n">
-        <v>106204</v>
+        <v>106207</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>131740539</v>
       </c>
       <c r="B16" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>131740540</v>
       </c>
       <c r="B17" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,45 +2287,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131736369</v>
+        <v>131737493</v>
       </c>
       <c r="B18" t="n">
-        <v>80286</v>
+        <v>96318</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>388</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nymyran Öst, Vb</t>
+          <t>Nymyrbäcken Sydost, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>714013</v>
+        <v>713904</v>
       </c>
       <c r="R18" t="n">
-        <v>7195603</v>
+        <v>7195596</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,45 +2388,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737493</v>
+        <v>131738024</v>
       </c>
       <c r="B19" t="n">
-        <v>96315</v>
+        <v>80422</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nymyrbäcken Sydost, Vb</t>
+          <t>Nymyran Öst, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>713904</v>
+        <v>713955</v>
       </c>
       <c r="R19" t="n">
-        <v>7195596</v>
+        <v>7195559</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131738024</v>
+        <v>131736369</v>
       </c>
       <c r="B20" t="n">
-        <v>80420</v>
+        <v>80288</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2500,21 +2500,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>713955</v>
+        <v>714013</v>
       </c>
       <c r="R20" t="n">
-        <v>7195559</v>
+        <v>7195603</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2593,7 +2593,7 @@
         <v>131734798</v>
       </c>
       <c r="B21" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131740660</v>
+        <v>131739483</v>
       </c>
       <c r="B22" t="n">
-        <v>83295</v>
+        <v>91892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2702,21 +2702,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>714030</v>
+        <v>714033</v>
       </c>
       <c r="R22" t="n">
-        <v>7195687</v>
+        <v>7195582</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131739483</v>
+        <v>131740660</v>
       </c>
       <c r="B23" t="n">
-        <v>91889</v>
+        <v>83297</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,21 +2803,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>714033</v>
+        <v>714030</v>
       </c>
       <c r="R23" t="n">
-        <v>7195582</v>
+        <v>7195687</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2896,7 +2896,7 @@
         <v>131736364</v>
       </c>
       <c r="B24" t="n">
-        <v>80286</v>
+        <v>80288</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>131736269</v>
       </c>
       <c r="B25" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>131738027</v>
       </c>
       <c r="B26" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>131736366</v>
       </c>
       <c r="B27" t="n">
-        <v>80286</v>
+        <v>80288</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>131737497</v>
       </c>
       <c r="B28" t="n">
-        <v>96315</v>
+        <v>96318</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>131738026</v>
       </c>
       <c r="B29" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,32 +3499,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131740421</v>
+        <v>131738578</v>
       </c>
       <c r="B30" t="n">
-        <v>80449</v>
+        <v>92080</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>1588</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>713954</v>
+        <v>714013</v>
       </c>
       <c r="R30" t="n">
-        <v>7195561</v>
+        <v>7195670</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,32 +3600,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131738578</v>
+        <v>131740421</v>
       </c>
       <c r="B31" t="n">
-        <v>92077</v>
+        <v>80451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1588</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>714013</v>
+        <v>713954</v>
       </c>
       <c r="R31" t="n">
-        <v>7195670</v>
+        <v>7195561</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131738025</v>
+        <v>131736268</v>
       </c>
       <c r="B32" t="n">
-        <v>80420</v>
+        <v>79317</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3712,34 +3712,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nymyran Öst, Vb</t>
+          <t>Nymyrbäcken Sydost, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>714035</v>
+        <v>713898</v>
       </c>
       <c r="R32" t="n">
-        <v>7195666</v>
+        <v>7195665</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3805,7 +3805,7 @@
         <v>131737494</v>
       </c>
       <c r="B33" t="n">
-        <v>96315</v>
+        <v>96318</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131736268</v>
+        <v>131738025</v>
       </c>
       <c r="B34" t="n">
-        <v>79315</v>
+        <v>80422</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,34 +3914,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nymyrbäcken Sydost, Vb</t>
+          <t>Nymyran Öst, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>713898</v>
+        <v>714035</v>
       </c>
       <c r="R34" t="n">
-        <v>7195665</v>
+        <v>7195666</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4007,7 +4007,7 @@
         <v>131740422</v>
       </c>
       <c r="B35" t="n">
-        <v>80449</v>
+        <v>80451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>131737495</v>
       </c>
       <c r="B36" t="n">
-        <v>96315</v>
+        <v>96318</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 29121-2024 artfynd.xlsx
+++ b/artfynd/A 29121-2024 artfynd.xlsx
@@ -3499,32 +3499,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131738578</v>
+        <v>131740421</v>
       </c>
       <c r="B30" t="n">
-        <v>92080</v>
+        <v>80451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1588</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>714013</v>
+        <v>713954</v>
       </c>
       <c r="R30" t="n">
-        <v>7195670</v>
+        <v>7195561</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,32 +3600,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131740421</v>
+        <v>131738578</v>
       </c>
       <c r="B31" t="n">
-        <v>80451</v>
+        <v>92080</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>1588</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>713954</v>
+        <v>714013</v>
       </c>
       <c r="R31" t="n">
-        <v>7195561</v>
+        <v>7195670</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 29121-2024 artfynd.xlsx
+++ b/artfynd/A 29121-2024 artfynd.xlsx
@@ -2287,45 +2287,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131737493</v>
+        <v>131736369</v>
       </c>
       <c r="B18" t="n">
-        <v>96318</v>
+        <v>80288</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2809</v>
+        <v>388</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nymyrbäcken Sydost, Vb</t>
+          <t>Nymyran Öst, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>713904</v>
+        <v>714013</v>
       </c>
       <c r="R18" t="n">
-        <v>7195596</v>
+        <v>7195603</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,45 +2388,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131738024</v>
+        <v>131737493</v>
       </c>
       <c r="B19" t="n">
-        <v>80422</v>
+        <v>96318</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nymyran Öst, Vb</t>
+          <t>Nymyrbäcken Sydost, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>713955</v>
+        <v>713904</v>
       </c>
       <c r="R19" t="n">
-        <v>7195559</v>
+        <v>7195596</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131736369</v>
+        <v>131738024</v>
       </c>
       <c r="B20" t="n">
-        <v>80288</v>
+        <v>80422</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2500,21 +2500,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>714013</v>
+        <v>713955</v>
       </c>
       <c r="R20" t="n">
-        <v>7195603</v>
+        <v>7195559</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3701,32 +3701,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131736268</v>
+        <v>131737494</v>
       </c>
       <c r="B32" t="n">
-        <v>79317</v>
+        <v>96318</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3736,10 +3736,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>713898</v>
+        <v>713914</v>
       </c>
       <c r="R32" t="n">
-        <v>7195665</v>
+        <v>7195565</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3802,32 +3802,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737494</v>
+        <v>131736268</v>
       </c>
       <c r="B33" t="n">
-        <v>96318</v>
+        <v>79317</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>713914</v>
+        <v>713898</v>
       </c>
       <c r="R33" t="n">
-        <v>7195565</v>
+        <v>7195665</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 29121-2024 artfynd.xlsx
+++ b/artfynd/A 29121-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131734797</v>
+        <v>131736364</v>
       </c>
       <c r="B2" t="n">
-        <v>99098</v>
+        <v>80344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>714013</v>
+        <v>714020</v>
       </c>
       <c r="R2" t="n">
-        <v>7195627</v>
+        <v>7195578</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131740575</v>
+        <v>131736365</v>
       </c>
       <c r="B3" t="n">
-        <v>106207</v>
+        <v>80344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nymyrbäcken Sydost, Vb</t>
+          <t>Nymyran Öst, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713929</v>
+        <v>714004</v>
       </c>
       <c r="R3" t="n">
-        <v>7195549</v>
+        <v>7195594</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131737496</v>
+        <v>131736366</v>
       </c>
       <c r="B4" t="n">
-        <v>96318</v>
+        <v>80344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>388</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>714009</v>
+        <v>714010</v>
       </c>
       <c r="R4" t="n">
-        <v>7195620</v>
+        <v>7195585</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131736695</v>
+        <v>131736367</v>
       </c>
       <c r="B5" t="n">
-        <v>80326</v>
+        <v>80344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>388</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>714003</v>
+        <v>714002</v>
       </c>
       <c r="R5" t="n">
         <v>7195588</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131739484</v>
+        <v>131736368</v>
       </c>
       <c r="B6" t="n">
-        <v>91892</v>
+        <v>80344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>388</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>714029</v>
+        <v>714012</v>
       </c>
       <c r="R6" t="n">
-        <v>7195738</v>
+        <v>7195598</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131740659</v>
+        <v>131736369</v>
       </c>
       <c r="B7" t="n">
-        <v>83297</v>
+        <v>80344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>388</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713964</v>
+        <v>714013</v>
       </c>
       <c r="R7" t="n">
-        <v>7195533</v>
+        <v>7195603</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131734796</v>
+        <v>131736370</v>
       </c>
       <c r="B8" t="n">
-        <v>99098</v>
+        <v>80344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>714036</v>
+        <v>714012</v>
       </c>
       <c r="R8" t="n">
-        <v>7195536</v>
+        <v>7195603</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131736368</v>
+        <v>131739483</v>
       </c>
       <c r="B9" t="n">
-        <v>80288</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>388</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>714012</v>
+        <v>714033</v>
       </c>
       <c r="R9" t="n">
-        <v>7195598</v>
+        <v>7195582</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131736044</v>
+        <v>131739484</v>
       </c>
       <c r="B10" t="n">
-        <v>91912</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,19 +1494,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1514,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>714023</v>
+        <v>714029</v>
       </c>
       <c r="R10" t="n">
-        <v>7195742</v>
+        <v>7195738</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131736365</v>
+        <v>131740539</v>
       </c>
       <c r="B11" t="n">
-        <v>80288</v>
+        <v>91985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>388</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>714004</v>
+        <v>714005</v>
       </c>
       <c r="R11" t="n">
-        <v>7195594</v>
+        <v>7195586</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1681,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131736370</v>
+        <v>131740540</v>
       </c>
       <c r="B12" t="n">
-        <v>80288</v>
+        <v>91985</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>388</v>
+        <v>1205</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1719,7 +1723,7 @@
         <v>714012</v>
       </c>
       <c r="R12" t="n">
-        <v>7195603</v>
+        <v>7195598</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131736367</v>
+        <v>131738578</v>
       </c>
       <c r="B13" t="n">
-        <v>80288</v>
+        <v>92167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>388</v>
+        <v>1588</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>714002</v>
+        <v>714013</v>
       </c>
       <c r="R13" t="n">
-        <v>7195588</v>
+        <v>7195670</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131732973</v>
+        <v>131737493</v>
       </c>
       <c r="B14" t="n">
-        <v>80457</v>
+        <v>96413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,34 +1898,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nymyran Öst, Vb</t>
+          <t>Nymyrbäcken Sydost, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>714024</v>
+        <v>713904</v>
       </c>
       <c r="R14" t="n">
-        <v>7195679</v>
+        <v>7195596</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1984,10 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131740576</v>
+        <v>131737494</v>
       </c>
       <c r="B15" t="n">
-        <v>106207</v>
+        <v>96413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1995,34 +1999,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nymyran Öst, Vb</t>
+          <t>Nymyrbäcken Sydost, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>714009</v>
+        <v>713914</v>
       </c>
       <c r="R15" t="n">
-        <v>7195593</v>
+        <v>7195565</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2085,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131740539</v>
+        <v>131737495</v>
       </c>
       <c r="B16" t="n">
-        <v>91903</v>
+        <v>96413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2096,34 +2100,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1205</v>
+        <v>2809</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nymyran Öst, Vb</t>
+          <t>Nymyrbäcken Sydost, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>714005</v>
+        <v>713961</v>
       </c>
       <c r="R16" t="n">
-        <v>7195586</v>
+        <v>7195523</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131740540</v>
+        <v>131737496</v>
       </c>
       <c r="B17" t="n">
-        <v>91903</v>
+        <v>96413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,21 +2201,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1205</v>
+        <v>2809</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2221,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>714012</v>
+        <v>714009</v>
       </c>
       <c r="R17" t="n">
-        <v>7195598</v>
+        <v>7195620</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2287,32 +2291,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131736369</v>
+        <v>131737497</v>
       </c>
       <c r="B18" t="n">
-        <v>80288</v>
+        <v>96413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>388</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>714013</v>
+        <v>714015</v>
       </c>
       <c r="R18" t="n">
-        <v>7195603</v>
+        <v>7195628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,32 +2392,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737493</v>
+        <v>131736268</v>
       </c>
       <c r="B19" t="n">
-        <v>96318</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2423,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>713904</v>
+        <v>713898</v>
       </c>
       <c r="R19" t="n">
-        <v>7195596</v>
+        <v>7195665</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,32 +2493,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131738024</v>
+        <v>131736269</v>
       </c>
       <c r="B20" t="n">
-        <v>80422</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2524,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>713955</v>
+        <v>713966</v>
       </c>
       <c r="R20" t="n">
-        <v>7195559</v>
+        <v>7195529</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2590,32 +2594,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131734798</v>
+        <v>131740659</v>
       </c>
       <c r="B21" t="n">
-        <v>99098</v>
+        <v>83358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2625,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>714024</v>
+        <v>713964</v>
       </c>
       <c r="R21" t="n">
-        <v>7195735</v>
+        <v>7195533</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,10 +2695,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131739483</v>
+        <v>131740660</v>
       </c>
       <c r="B22" t="n">
-        <v>91892</v>
+        <v>83358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2702,21 +2706,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2726,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>714033</v>
+        <v>714030</v>
       </c>
       <c r="R22" t="n">
-        <v>7195582</v>
+        <v>7195687</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,32 +2796,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131740660</v>
+        <v>131736695</v>
       </c>
       <c r="B23" t="n">
-        <v>83297</v>
+        <v>80382</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2827,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>714030</v>
+        <v>714003</v>
       </c>
       <c r="R23" t="n">
-        <v>7195687</v>
+        <v>7195588</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131736364</v>
+        <v>131738024</v>
       </c>
       <c r="B24" t="n">
-        <v>80288</v>
+        <v>80488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2904,21 +2908,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2928,10 +2932,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>714020</v>
+        <v>713955</v>
       </c>
       <c r="R24" t="n">
-        <v>7195578</v>
+        <v>7195559</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,10 +2998,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131736269</v>
+        <v>131738025</v>
       </c>
       <c r="B25" t="n">
-        <v>79317</v>
+        <v>80488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,21 +3009,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3029,10 +3033,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>713966</v>
+        <v>714035</v>
       </c>
       <c r="R25" t="n">
-        <v>7195529</v>
+        <v>7195666</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3095,10 +3099,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131738027</v>
+        <v>131738026</v>
       </c>
       <c r="B26" t="n">
-        <v>80422</v>
+        <v>80488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3130,10 +3134,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>714054</v>
+        <v>714025</v>
       </c>
       <c r="R26" t="n">
-        <v>7195699</v>
+        <v>7195680</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3196,10 +3200,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131736366</v>
+        <v>131738027</v>
       </c>
       <c r="B27" t="n">
-        <v>80288</v>
+        <v>80488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3207,21 +3211,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3231,10 +3235,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>714010</v>
+        <v>714054</v>
       </c>
       <c r="R27" t="n">
-        <v>7195585</v>
+        <v>7195699</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3297,10 +3301,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131737497</v>
+        <v>131740421</v>
       </c>
       <c r="B28" t="n">
-        <v>96318</v>
+        <v>80493</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3308,21 +3312,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3332,10 +3336,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>714015</v>
+        <v>713954</v>
       </c>
       <c r="R28" t="n">
-        <v>7195628</v>
+        <v>7195561</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3398,32 +3402,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131738026</v>
+        <v>131740422</v>
       </c>
       <c r="B29" t="n">
-        <v>80422</v>
+        <v>80493</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3433,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>714025</v>
+        <v>714023</v>
       </c>
       <c r="R29" t="n">
-        <v>7195680</v>
+        <v>7195678</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,10 +3503,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131740421</v>
+        <v>131732973</v>
       </c>
       <c r="B30" t="n">
-        <v>80451</v>
+        <v>80499</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3510,21 +3514,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3534,10 +3538,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>713954</v>
+        <v>714024</v>
       </c>
       <c r="R30" t="n">
-        <v>7195561</v>
+        <v>7195679</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,32 +3604,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131738578</v>
+        <v>131734796</v>
       </c>
       <c r="B31" t="n">
-        <v>92080</v>
+        <v>99195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3635,10 +3639,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>714013</v>
+        <v>714036</v>
       </c>
       <c r="R31" t="n">
-        <v>7195670</v>
+        <v>7195536</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3701,45 +3705,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737494</v>
+        <v>131734797</v>
       </c>
       <c r="B32" t="n">
-        <v>96318</v>
+        <v>99195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nymyrbäcken Sydost, Vb</t>
+          <t>Nymyran Öst, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>713914</v>
+        <v>714013</v>
       </c>
       <c r="R32" t="n">
-        <v>7195565</v>
+        <v>7195627</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3802,45 +3806,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131736268</v>
+        <v>131734798</v>
       </c>
       <c r="B33" t="n">
-        <v>79317</v>
+        <v>99195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nymyrbäcken Sydost, Vb</t>
+          <t>Nymyran Öst, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>713898</v>
+        <v>714024</v>
       </c>
       <c r="R33" t="n">
-        <v>7195665</v>
+        <v>7195735</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3903,45 +3907,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131738025</v>
+        <v>131740575</v>
       </c>
       <c r="B34" t="n">
-        <v>80422</v>
+        <v>106309</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nymyran Öst, Vb</t>
+          <t>Nymyrbäcken Sydost, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>714035</v>
+        <v>713929</v>
       </c>
       <c r="R34" t="n">
-        <v>7195666</v>
+        <v>7195549</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4004,10 +4008,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131740422</v>
+        <v>131740576</v>
       </c>
       <c r="B35" t="n">
-        <v>80451</v>
+        <v>106309</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4015,21 +4019,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4039,10 +4043,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>714023</v>
+        <v>714009</v>
       </c>
       <c r="R35" t="n">
-        <v>7195678</v>
+        <v>7195593</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4098,107 +4102,6 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>131737495</v>
-      </c>
-      <c r="B36" t="n">
-        <v>96318</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>2809</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Mörk husmossa</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Hylocomiastrum umbratum</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Nymyrbäcken Sydost, Vb</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>713961</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7195523</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Helene Andersson</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Elin Kollberg</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
